--- a/document/modelos.xlsx
+++ b/document/modelos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camilaortiz/Dropbox/PEG/BigData/ProblemSet2_G10/document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F13796A5-2727-E74A-9C3B-5D152EF7AE7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78243E0C-97D6-D542-A07B-615E07474ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17400" yWindow="740" windowWidth="24960" windowHeight="16780" xr2:uid="{0E35A591-4511-AB40-9BF9-7C05772B802C}"/>
+    <workbookView xWindow="400" yWindow="740" windowWidth="11660" windowHeight="16780" xr2:uid="{0E35A591-4511-AB40-9BF9-7C05772B802C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>Variables</t>
   </si>
@@ -80,9 +80,6 @@
     <t>N_pet</t>
   </si>
   <si>
-    <t>N_menpres</t>
-  </si>
-  <si>
     <t>N_mayor_dependiente</t>
   </si>
   <si>
@@ -123,6 +120,12 @@
   </si>
   <si>
     <t>Modelo 7</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>N_menores</t>
   </si>
 </sst>
 </file>
@@ -171,9 +174,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -512,40 +518,41 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -560,16 +567,25 @@
       <c r="A7" t="s">
         <v>1</v>
       </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>2</v>
       </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
+      <c r="B9" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -585,16 +601,25 @@
       <c r="A12" t="s">
         <v>6</v>
       </c>
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
+      <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>8</v>
       </c>
+      <c r="B14" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -606,49 +631,55 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/document/modelos.xlsx
+++ b/document/modelos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camilaortiz/Dropbox/PEG/BigData/ProblemSet2_G10/document/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\1. General\3. Académico\3. Uniandes\Machine Learning + BD\Repos_GitHub\ProblemSet2_G10\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78243E0C-97D6-D542-A07B-615E07474ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E2AC6C-F79B-457E-AACD-E455D396C023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="740" windowWidth="11660" windowHeight="16780" xr2:uid="{0E35A591-4511-AB40-9BF9-7C05772B802C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{0E35A591-4511-AB40-9BF9-7C05772B802C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>Variables</t>
   </si>
@@ -126,6 +126,15 @@
   </si>
   <si>
     <t>N_menores</t>
+  </si>
+  <si>
+    <t>logit</t>
+  </si>
+  <si>
+    <t>regresión lineal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EN </t>
   </si>
 </sst>
 </file>
@@ -515,13 +524,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7943A469-06BA-124A-A75F-874F7DAFF4B5}">
   <dimension ref="A2:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="10.83203125" style="2"/>
+    <col min="2" max="2" width="10.796875" style="2"/>
+    <col min="3" max="3" width="13.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="10.796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>19</v>
@@ -545,25 +556,34 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -571,7 +591,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -579,7 +599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -587,17 +607,17 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -605,7 +625,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -613,7 +633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -621,22 +641,22 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -644,17 +664,17 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -662,22 +682,22 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>

--- a/document/modelos.xlsx
+++ b/document/modelos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\1. General\3. Académico\3. Uniandes\Machine Learning + BD\Repos_GitHub\ProblemSet2_G10\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E2AC6C-F79B-457E-AACD-E455D396C023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD763FE2-E1D8-4977-9096-A23E98335ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{0E35A591-4511-AB40-9BF9-7C05772B802C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
   <si>
     <t>Variables</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t xml:space="preserve">EN </t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -590,6 +593,9 @@
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="D7" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -606,16 +612,25 @@
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="D9" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
+      <c r="D10" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
+      <c r="D11" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -624,6 +639,9 @@
       <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="D12" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -632,6 +650,9 @@
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="D13" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -640,6 +661,9 @@
       <c r="B14" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="D14" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -651,12 +675,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -664,42 +688,57 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D21" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D22" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D23" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D24" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/document/modelos.xlsx
+++ b/document/modelos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\1. General\3. Académico\3. Uniandes\Machine Learning + BD\Repos_GitHub\ProblemSet2_G10\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD763FE2-E1D8-4977-9096-A23E98335ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52B9F3E-43BB-413A-B4E3-B550DE616BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{0E35A591-4511-AB40-9BF9-7C05772B802C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
   <si>
     <t>Variables</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>boosting</t>
   </si>
 </sst>
 </file>
@@ -577,6 +580,9 @@
       <c r="D4" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="F4" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -596,6 +602,9 @@
       <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="F7" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -615,6 +624,9 @@
       <c r="D9" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="F9" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -623,6 +635,9 @@
       <c r="D10" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="F10" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -631,6 +646,9 @@
       <c r="D11" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="F11" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -642,6 +660,9 @@
       <c r="D12" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="F12" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -664,6 +685,9 @@
       <c r="D14" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="F14" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -675,12 +699,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -688,17 +712,20 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F20" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -708,8 +735,11 @@
       <c r="D21" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F21" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -717,15 +747,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F23" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -733,11 +766,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>33</v>
       </c>
     </row>
